--- a/route/Blue-Yellow Buses (Private)/77a(nobata).xlsx
+++ b/route/Blue-Yellow Buses (Private)/77a(nobata).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arpan\Desktop\testing_gps_wifi_esp8266\Blue-Yellow Buses (Private)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arpan\Desktop\NEXBUS_LIVE\route\Blue-Yellow Buses (Private)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71BBAE8F-6261-44AA-9423-3597A1A6462F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B90B5C8-4DE4-4BF3-8697-09CEECB87DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{170A076F-52B9-491F-9C3B-01CA07485FE0}"/>
+    <workbookView xWindow="10200" yWindow="0" windowWidth="10200" windowHeight="10920" xr2:uid="{170A076F-52B9-491F-9C3B-01CA07485FE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -182,9 +182,6 @@
     <t>Puratan Dakghar(22°30'27.6"N 88°15'30.9"E)</t>
   </si>
   <si>
-    <t>Santoshpur (Down)(22°30'47.6"N 88°16'17.7"E)</t>
-  </si>
-  <si>
     <t>Jolkol(22°30'33.5"N 88°15'45.0"E)</t>
   </si>
   <si>
@@ -327,6 +324,9 @@
   </si>
   <si>
     <t>Birlapur Bus Stand(22°25'41.8"N 88°09'14.5"E)</t>
+  </si>
+  <si>
+    <t>Santoshpur (Down)(22°30'45.9"N 88°16'07.4"E)</t>
   </si>
 </sst>
 </file>
@@ -937,199 +937,199 @@
         <v>46</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
